--- a/data/macro/China/China CPI.xlsx
+++ b/data/macro/China/China CPI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/AlternativeData/data/macro/China/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B007CE9E-82A2-DA48-9463-8B74CA393B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65384EEB-A1D4-45BA-8C1A-C8D06984085F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6700" yWindow="3260" windowWidth="27640" windowHeight="16680" xr2:uid="{C2D375C2-0F84-A74D-B79F-82236B74EEEF}"/>
+    <workbookView xWindow="6705" yWindow="3255" windowWidth="27645" windowHeight="16680" xr2:uid="{C2D375C2-0F84-A74D-B79F-82236B74EEEF}"/>
   </bookViews>
   <sheets>
     <sheet name="CNCPIYOY" sheetId="1" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="14">
   <si>
     <t>Time</t>
   </si>
@@ -77,27 +66,31 @@
   <si>
     <t>monthly</t>
   </si>
+  <si>
+    <t>UTC+8</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="171" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -105,15 +98,22 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -143,23 +143,23 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -168,8 +168,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -502,15 +502,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A2DF88-805C-2E4E-A3EC-9F545567B7EC}">
   <dimension ref="A1:I481"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="10.83203125" style="5"/>
-    <col min="3" max="3" width="10.83203125" style="10"/>
-    <col min="4" max="4" width="10.83203125" style="6"/>
-    <col min="5" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="2" width="10.77734375" style="5"/>
+    <col min="3" max="3" width="10.77734375" style="10"/>
+    <col min="4" max="4" width="10.77734375" style="6"/>
+    <col min="5" max="16384" width="10.77734375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>7</v>
       </c>
@@ -534,7 +534,7 @@
       </c>
       <c r="I1" s="2"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>31413</v>
       </c>
@@ -545,7 +545,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2" s="3">
         <v>7.0999999999999994E-2</v>
@@ -559,7 +559,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>31444</v>
       </c>
@@ -583,7 +583,7 @@
       </c>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>31472</v>
       </c>
@@ -607,7 +607,7 @@
       </c>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>31503</v>
       </c>
@@ -631,7 +631,7 @@
       </c>
       <c r="H5" s="4"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>31533</v>
       </c>
@@ -655,7 +655,7 @@
       </c>
       <c r="H6" s="4"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>31564</v>
       </c>
@@ -679,7 +679,7 @@
       </c>
       <c r="H7" s="4"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>31594</v>
       </c>
@@ -703,7 +703,7 @@
       </c>
       <c r="H8" s="4"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>31625</v>
       </c>
@@ -727,7 +727,7 @@
       </c>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>31656</v>
       </c>
@@ -751,7 +751,7 @@
       </c>
       <c r="H10" s="4"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>31686</v>
       </c>
@@ -775,7 +775,7 @@
       </c>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>31717</v>
       </c>
@@ -799,7 +799,7 @@
       </c>
       <c r="H12" s="4"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>31747</v>
       </c>
@@ -823,7 +823,7 @@
       </c>
       <c r="H13" s="4"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>31778</v>
       </c>
@@ -847,7 +847,7 @@
       </c>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>31809</v>
       </c>
@@ -871,7 +871,7 @@
       </c>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>31837</v>
       </c>
@@ -895,7 +895,7 @@
       </c>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>31868</v>
       </c>
@@ -919,7 +919,7 @@
       </c>
       <c r="H17" s="4"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>31898</v>
       </c>
@@ -943,7 +943,7 @@
       </c>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>31929</v>
       </c>
@@ -967,7 +967,7 @@
       </c>
       <c r="H19" s="4"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>31959</v>
       </c>
@@ -991,7 +991,7 @@
       </c>
       <c r="H20" s="4"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>31990</v>
       </c>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="H21" s="4"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>32021</v>
       </c>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>32051</v>
       </c>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="H23" s="4"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>32082</v>
       </c>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="H24" s="4"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>32112</v>
       </c>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>32143</v>
       </c>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="H26" s="4"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>32174</v>
       </c>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>32203</v>
       </c>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="H28" s="4"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>32234</v>
       </c>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="H29" s="4"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>32264</v>
       </c>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="H30" s="4"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>32295</v>
       </c>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H31" s="4"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>32325</v>
       </c>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>32356</v>
       </c>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="H33" s="4"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>32387</v>
       </c>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="H34" s="4"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>32417</v>
       </c>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H35" s="4"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>32448</v>
       </c>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="H36" s="4"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>32478</v>
       </c>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="H37" s="4"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>32509</v>
       </c>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="H38" s="4"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>32540</v>
       </c>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>32568</v>
       </c>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="H40" s="4"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>32599</v>
       </c>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="H41" s="4"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>32629</v>
       </c>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="H42" s="4"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>32660</v>
       </c>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="H43" s="4"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>32690</v>
       </c>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="H44" s="4"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>32721</v>
       </c>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="H45" s="4"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>32752</v>
       </c>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="H46" s="4"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>32782</v>
       </c>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="H47" s="4"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>32813</v>
       </c>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="H48" s="4"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>32843</v>
       </c>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="H49" s="4"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>32874</v>
       </c>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="H50" s="4"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>32905</v>
       </c>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="H51" s="4"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>32933</v>
       </c>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H52" s="4"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>32964</v>
       </c>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="H53" s="4"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>32994</v>
       </c>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H54" s="4"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>33025</v>
       </c>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="H55" s="4"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>33055</v>
       </c>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="H56" s="4"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>33086</v>
       </c>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="H57" s="4"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>33117</v>
       </c>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="H58" s="4"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>33147</v>
       </c>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="H59" s="4"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>33178</v>
       </c>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="H60" s="4"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>33208</v>
       </c>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="H61" s="4"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>33239</v>
       </c>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="H62" s="4"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>33270</v>
       </c>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="H63" s="4"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>33298</v>
       </c>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="H64" s="4"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>33329</v>
       </c>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="H65" s="4"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>33359</v>
       </c>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="H66" s="4"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>33390</v>
       </c>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="H67" s="4"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>33420</v>
       </c>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="H68" s="4"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>33451</v>
       </c>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="H69" s="4"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>33482</v>
       </c>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="H70" s="4"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>33512</v>
       </c>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="H71" s="4"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>33543</v>
       </c>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="H72" s="4"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>33573</v>
       </c>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H73" s="4"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>33604</v>
       </c>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="H74" s="4"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>33635</v>
       </c>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="H75" s="4"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>33664</v>
       </c>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="H76" s="4"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>33695</v>
       </c>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="H77" s="4"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>33725</v>
       </c>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="H78" s="4"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>33756</v>
       </c>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="H79" s="4"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>33786</v>
       </c>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="H80" s="4"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>33817</v>
       </c>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="H81" s="4"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>33848</v>
       </c>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="H82" s="4"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>33878</v>
       </c>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="H83" s="4"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>33909</v>
       </c>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="H84" s="4"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>33939</v>
       </c>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="H85" s="4"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>33970</v>
       </c>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H86" s="4"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>34001</v>
       </c>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="H87" s="4"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>34029</v>
       </c>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H88" s="4"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>34060</v>
       </c>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="H89" s="4"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>34090</v>
       </c>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="H90" s="4"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>34121</v>
       </c>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="H91" s="4"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>34151</v>
       </c>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="H92" s="4"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>34182</v>
       </c>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="H93" s="4"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>34213</v>
       </c>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="H94" s="4"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>34243</v>
       </c>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H95" s="4"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <v>34274</v>
       </c>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="H96" s="4"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>34304</v>
       </c>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="H97" s="4"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>34335</v>
       </c>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="H98" s="4"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>34366</v>
       </c>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="H99" s="4"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>34394</v>
       </c>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="H100" s="4"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>34425</v>
       </c>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="H101" s="4"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>34455</v>
       </c>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="H102" s="4"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>34486</v>
       </c>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="H103" s="4"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>34516</v>
       </c>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="H104" s="4"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>34547</v>
       </c>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="H105" s="4"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>34578</v>
       </c>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="H106" s="4"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>34608</v>
       </c>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="H107" s="4"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>34639</v>
       </c>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="H108" s="4"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <v>34669</v>
       </c>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="H109" s="4"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>34700</v>
       </c>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H110" s="4"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>34731</v>
       </c>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="H111" s="4"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>34759</v>
       </c>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="H112" s="4"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>34790</v>
       </c>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="H113" s="4"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>34820</v>
       </c>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H114" s="4"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>34851</v>
       </c>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="H115" s="4"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>34881</v>
       </c>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="H116" s="4"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>34912</v>
       </c>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="H117" s="4"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>34943</v>
       </c>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="H118" s="4"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>34973</v>
       </c>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="H119" s="4"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>35004</v>
       </c>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="H120" s="4"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>35034</v>
       </c>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="H121" s="4"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
         <v>35065</v>
       </c>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="H122" s="4"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>35096</v>
       </c>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="H123" s="4"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>35125</v>
       </c>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="H124" s="4"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>35156</v>
       </c>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="H125" s="4"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>35186</v>
       </c>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="H126" s="4"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>35217</v>
       </c>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="H127" s="4"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <v>35247</v>
       </c>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="H128" s="4"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>35278</v>
       </c>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="H129" s="4"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>35309</v>
       </c>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="H130" s="4"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>35339</v>
       </c>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="H131" s="4"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <v>35370</v>
       </c>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="H132" s="4"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>35400</v>
       </c>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H133" s="4"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>35431</v>
       </c>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="H134" s="4"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>35462</v>
       </c>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="H135" s="4"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <v>35490</v>
       </c>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="H136" s="4"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <v>35521</v>
       </c>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="H137" s="4"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <v>35551</v>
       </c>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="H138" s="4"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <v>35582</v>
       </c>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H139" s="4"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
         <v>35612</v>
       </c>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="H140" s="4"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
         <v>35643</v>
       </c>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="H141" s="4"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
         <v>35674</v>
       </c>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="H142" s="4"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" s="5">
         <v>35704</v>
       </c>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="H143" s="4"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
         <v>35735</v>
       </c>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="H144" s="4"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <v>35765</v>
       </c>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="H145" s="4"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
         <v>35796</v>
       </c>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="H146" s="4"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <v>35827</v>
       </c>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="H147" s="4"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
         <v>35855</v>
       </c>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="H148" s="4"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <v>35886</v>
       </c>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H149" s="4"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" s="5">
         <v>35916</v>
       </c>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="H150" s="4"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
         <v>35947</v>
       </c>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="H151" s="4"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
         <v>35977</v>
       </c>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H152" s="4"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" s="5">
         <v>36008</v>
       </c>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H153" s="4"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <v>36039</v>
       </c>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="H154" s="4"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
         <v>36069</v>
       </c>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="H155" s="4"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
         <v>36100</v>
       </c>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="H156" s="4"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" s="5">
         <v>36130</v>
       </c>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="H157" s="4"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="5">
         <v>36161</v>
       </c>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="H158" s="4"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" s="5">
         <v>36192</v>
       </c>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="H159" s="4"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" s="5">
         <v>36220</v>
       </c>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H160" s="4"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="5">
         <v>36251</v>
       </c>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="H161" s="4"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="5">
         <v>36281</v>
       </c>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="H162" s="4"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" s="5">
         <v>36312</v>
       </c>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="H163" s="4"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="5">
         <v>36342</v>
       </c>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="H164" s="4"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" s="5">
         <v>36373</v>
       </c>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="H165" s="4"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" s="5">
         <v>36404</v>
       </c>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="H166" s="4"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="5">
         <v>36434</v>
       </c>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="H167" s="4"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="5">
         <v>36465</v>
       </c>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="H168" s="4"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
         <v>36495</v>
       </c>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="H169" s="4"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="5">
         <v>36526</v>
       </c>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="H170" s="4"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="5">
         <v>36557</v>
       </c>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H171" s="4"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
         <v>36586</v>
       </c>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="H172" s="4"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="5">
         <v>36617</v>
       </c>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="H173" s="4"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="5">
         <v>36647</v>
       </c>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="H174" s="4"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="5">
         <v>36678</v>
       </c>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="H175" s="4"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="5">
         <v>36708</v>
       </c>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="H176" s="4"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="5">
         <v>36739</v>
       </c>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="H177" s="4"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="5">
         <v>36770</v>
       </c>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="H178" s="4"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="5">
         <v>36800</v>
       </c>
@@ -4807,7 +4807,7 @@
       </c>
       <c r="H179" s="4"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="5">
         <v>36831</v>
       </c>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="H180" s="4"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="5">
         <v>36861</v>
       </c>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="H181" s="4"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="5">
         <v>36892</v>
       </c>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="H182" s="4"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="5">
         <v>36923</v>
       </c>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="H183" s="4"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="5">
         <v>36951</v>
       </c>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="H184" s="4"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="5">
         <v>36982</v>
       </c>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="H185" s="4"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="5">
         <v>37012</v>
       </c>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="H186" s="4"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" s="5">
         <v>37043</v>
       </c>
@@ -4999,7 +4999,7 @@
       </c>
       <c r="H187" s="4"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="5">
         <v>37073</v>
       </c>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="H188" s="4"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" s="5">
         <v>37104</v>
       </c>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="H189" s="4"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="5">
         <v>37135</v>
       </c>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H190" s="4"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="5">
         <v>37165</v>
       </c>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H191" s="4"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="5">
         <v>37196</v>
       </c>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="H192" s="4"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="5">
         <v>37226</v>
       </c>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="H193" s="4"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="5">
         <v>37257</v>
       </c>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="H194" s="4"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="5">
         <v>37288</v>
       </c>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="H195" s="4"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="5">
         <v>37316</v>
       </c>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="H196" s="4"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="5">
         <v>37347</v>
       </c>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="H197" s="4"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="5">
         <v>37377</v>
       </c>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="H198" s="4"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" s="5">
         <v>37408</v>
       </c>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="H199" s="4"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="5">
         <v>37438</v>
       </c>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="H200" s="4"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="5">
         <v>37469</v>
       </c>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="H201" s="4"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="5">
         <v>37500</v>
       </c>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="H202" s="4"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="5">
         <v>37530</v>
       </c>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="H203" s="4"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="5">
         <v>37561</v>
       </c>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="H204" s="4"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="5">
         <v>37591</v>
       </c>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="H205" s="4"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="5">
         <v>37622</v>
       </c>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="H206" s="4"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="5">
         <v>37653</v>
       </c>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="H207" s="4"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="5">
         <v>37681</v>
       </c>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="H208" s="4"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="5">
         <v>37712</v>
       </c>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="H209" s="4"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="5">
         <v>37742</v>
       </c>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H210" s="4"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" s="5">
         <v>37773</v>
       </c>
@@ -5575,7 +5575,7 @@
       </c>
       <c r="H211" s="4"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="5">
         <v>37803</v>
       </c>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="H212" s="4"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="5">
         <v>37834</v>
       </c>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="H213" s="4"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="5">
         <v>37865</v>
       </c>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="H214" s="4"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="5">
         <v>37895</v>
       </c>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="H215" s="4"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="5">
         <v>37926</v>
       </c>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="H216" s="4"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="5">
         <v>37956</v>
       </c>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="H217" s="4"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="5">
         <v>37987</v>
       </c>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="H218" s="4"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="5">
         <v>38018</v>
       </c>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="H219" s="4"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="5">
         <v>38047</v>
       </c>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="H220" s="4"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="5">
         <v>38078</v>
       </c>
@@ -5815,7 +5815,7 @@
       </c>
       <c r="H221" s="4"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="5">
         <v>38108</v>
       </c>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="H222" s="4"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="5">
         <v>38139</v>
       </c>
@@ -5863,7 +5863,7 @@
       </c>
       <c r="H223" s="4"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="5">
         <v>38169</v>
       </c>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="H224" s="4"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="5">
         <v>38200</v>
       </c>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="H225" s="4"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="5">
         <v>38231</v>
       </c>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="H226" s="4"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" s="5">
         <v>38261</v>
       </c>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="H227" s="4"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="5">
         <v>38292</v>
       </c>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="H228" s="4"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="5">
         <v>38322</v>
       </c>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="H229" s="4"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="5">
         <v>38353</v>
       </c>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="H230" s="4"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="5">
         <v>38384</v>
       </c>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="H231" s="4"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="5">
         <v>38412</v>
       </c>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="H232" s="4"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="5">
         <v>38443</v>
       </c>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="H233" s="4"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="5">
         <v>38473</v>
       </c>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H234" s="4"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="5">
         <v>38504</v>
       </c>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="H235" s="4"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="5">
         <v>38534</v>
       </c>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="H236" s="4"/>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="5">
         <v>38565</v>
       </c>
@@ -6199,7 +6199,7 @@
       </c>
       <c r="H237" s="4"/>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="5">
         <v>38596</v>
       </c>
@@ -6223,7 +6223,7 @@
       </c>
       <c r="H238" s="4"/>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="5">
         <v>38626</v>
       </c>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="H239" s="4"/>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" s="5">
         <v>38657</v>
       </c>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="H240" s="4"/>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="5">
         <v>38687</v>
       </c>
@@ -6295,7 +6295,7 @@
       </c>
       <c r="H241" s="4"/>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" s="5">
         <v>38718</v>
       </c>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="H242" s="4"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="5">
         <v>38749</v>
       </c>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="H243" s="4"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="5">
         <v>38777</v>
       </c>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="H244" s="4"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="5">
         <v>38808</v>
       </c>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="H245" s="4"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="5">
         <v>38838</v>
       </c>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="H246" s="4"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="5">
         <v>38869</v>
       </c>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="H247" s="4"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="5">
         <v>38899</v>
       </c>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="H248" s="4"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="5">
         <v>38930</v>
       </c>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="H249" s="4"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="5">
         <v>38961</v>
       </c>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="H250" s="4"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="5">
         <v>38991</v>
       </c>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="H251" s="4"/>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="5">
         <v>39022</v>
       </c>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="H252" s="4"/>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="5">
         <v>39052</v>
       </c>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="H253" s="4"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="5">
         <v>39083</v>
       </c>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="H254" s="4"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="5">
         <v>39114</v>
       </c>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="H255" s="4"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="5">
         <v>39142</v>
       </c>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="H256" s="4"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="5">
         <v>39173</v>
       </c>
@@ -6679,7 +6679,7 @@
       </c>
       <c r="H257" s="4"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="5">
         <v>39203</v>
       </c>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="H258" s="4"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="5">
         <v>39234</v>
       </c>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="H259" s="4"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="5">
         <v>39264</v>
       </c>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="H260" s="4"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="5">
         <v>39295</v>
       </c>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="H261" s="4"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="5">
         <v>39326</v>
       </c>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="H262" s="4"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="5">
         <v>39356</v>
       </c>
@@ -6823,7 +6823,7 @@
       </c>
       <c r="H263" s="4"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="5">
         <v>39387</v>
       </c>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="H264" s="4"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="5">
         <v>39417</v>
       </c>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="H265" s="4"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="5">
         <v>39448</v>
       </c>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="H266" s="4"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" s="5">
         <v>39479</v>
       </c>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="H267" s="4"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="5">
         <v>39508</v>
       </c>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="H268" s="4"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="5">
         <v>39539</v>
       </c>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="H269" s="4"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="5">
         <v>39569</v>
       </c>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="H270" s="4"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" s="5">
         <v>39600</v>
       </c>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H271" s="4"/>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="5">
         <v>39630</v>
       </c>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="H272" s="4"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="5">
         <v>39661</v>
       </c>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="H273" s="4"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" s="5">
         <v>39692</v>
       </c>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="H274" s="4"/>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" s="5">
         <v>39722</v>
       </c>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="H275" s="4"/>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" s="5">
         <v>39753</v>
       </c>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="H276" s="4"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" s="5">
         <v>39783</v>
       </c>
@@ -7159,7 +7159,7 @@
       </c>
       <c r="H277" s="4"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" s="5">
         <v>39814</v>
       </c>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="H278" s="4"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" s="5">
         <v>39845</v>
       </c>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="H279" s="4"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" s="5">
         <v>39873</v>
       </c>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="H280" s="4"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="5">
         <v>39904</v>
       </c>
@@ -7255,7 +7255,7 @@
       </c>
       <c r="H281" s="4"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="5">
         <v>39934</v>
       </c>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="H282" s="4"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" s="5">
         <v>39965</v>
       </c>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="H283" s="4"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="5">
         <v>39995</v>
       </c>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="H284" s="4"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="5">
         <v>40026</v>
       </c>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="H285" s="4"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" s="5">
         <v>40057</v>
       </c>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="H286" s="4"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" s="5">
         <v>40087</v>
       </c>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="H287" s="4"/>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" s="5">
         <v>40118</v>
       </c>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="H288" s="4"/>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="5">
         <v>40148</v>
       </c>
@@ -7447,7 +7447,7 @@
       </c>
       <c r="H289" s="4"/>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="5">
         <v>40179</v>
       </c>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="H290" s="4"/>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="5">
         <v>40210</v>
       </c>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="H291" s="4"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="5">
         <v>40238</v>
       </c>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="H292" s="4"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="5">
         <v>40269</v>
       </c>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="H293" s="4"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="5">
         <v>40299</v>
       </c>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="H294" s="4"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="5">
         <v>40330</v>
       </c>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="H295" s="4"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="5">
         <v>40360</v>
       </c>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="H296" s="4"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="5">
         <v>40391</v>
       </c>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="H297" s="4"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="5">
         <v>40422</v>
       </c>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="H298" s="4"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="5">
         <v>40452</v>
       </c>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="H299" s="4"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="5">
         <v>40483</v>
       </c>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="H300" s="4"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" s="5">
         <v>40513</v>
       </c>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="H301" s="4"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="5">
         <v>40544</v>
       </c>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="H302" s="4"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="5">
         <v>40575</v>
       </c>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="H303" s="4"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" s="5">
         <v>40603</v>
       </c>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="H304" s="4"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" s="5">
         <v>40634</v>
       </c>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="H305" s="4"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" s="5">
         <v>40664</v>
       </c>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="H306" s="4"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" s="5">
         <v>40695</v>
       </c>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="H307" s="4"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" s="5">
         <v>40725</v>
       </c>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="H308" s="4"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" s="5">
         <v>40756</v>
       </c>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="H309" s="4"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="5">
         <v>40787</v>
       </c>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="H310" s="4"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="5">
         <v>40817</v>
       </c>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="H311" s="4"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" s="5">
         <v>40848</v>
       </c>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="H312" s="4"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" s="5">
         <v>40878</v>
       </c>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="H313" s="4"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" s="5">
         <v>40909</v>
       </c>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="H314" s="4"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" s="5">
         <v>40940</v>
       </c>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="H315" s="4"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" s="5">
         <v>40969</v>
       </c>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="H316" s="4"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="5">
         <v>41000</v>
       </c>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="H317" s="4"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="5">
         <v>41030</v>
       </c>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="H318" s="4"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="5">
         <v>41061</v>
       </c>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="H319" s="4"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" s="5">
         <v>41091</v>
       </c>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H320" s="4"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" s="5">
         <v>41122</v>
       </c>
@@ -8215,7 +8215,7 @@
       </c>
       <c r="H321" s="4"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="5">
         <v>41153</v>
       </c>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="H322" s="4"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="5">
         <v>41183</v>
       </c>
@@ -8263,7 +8263,7 @@
       </c>
       <c r="H323" s="4"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" s="5">
         <v>41214</v>
       </c>
@@ -8287,7 +8287,7 @@
       </c>
       <c r="H324" s="4"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" s="5">
         <v>41244</v>
       </c>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="H325" s="4"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" s="5">
         <v>41275</v>
       </c>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="H326" s="4"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" s="5">
         <v>41306</v>
       </c>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="H327" s="4"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" s="5">
         <v>41334</v>
       </c>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="H328" s="4"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" s="5">
         <v>41365</v>
       </c>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="H329" s="4"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" s="5">
         <v>41395</v>
       </c>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="H330" s="4"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="5">
         <v>41426</v>
       </c>
@@ -8455,7 +8455,7 @@
       </c>
       <c r="H331" s="4"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="5">
         <v>41456</v>
       </c>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H332" s="4"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="5">
         <v>41487</v>
       </c>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="H333" s="4"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" s="5">
         <v>41518</v>
       </c>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="H334" s="4"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" s="5">
         <v>41548</v>
       </c>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="H335" s="4"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" s="5">
         <v>41579</v>
       </c>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="H336" s="4"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" s="5">
         <v>41609</v>
       </c>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="H337" s="4"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" s="5">
         <v>41640</v>
       </c>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="H338" s="4"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="5">
         <v>41671</v>
       </c>
@@ -8647,7 +8647,7 @@
       </c>
       <c r="H339" s="4"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" s="5">
         <v>41699</v>
       </c>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="H340" s="4"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" s="5">
         <v>41730</v>
       </c>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="H341" s="4"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" s="5">
         <v>41760</v>
       </c>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="H342" s="4"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="5">
         <v>41791</v>
       </c>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="H343" s="4"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" s="5">
         <v>41821</v>
       </c>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="H344" s="4"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="5">
         <v>41852</v>
       </c>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="H345" s="4"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="5">
         <v>41883</v>
       </c>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="H346" s="4"/>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" s="5">
         <v>41913</v>
       </c>
@@ -8839,7 +8839,7 @@
       </c>
       <c r="H347" s="4"/>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" s="5">
         <v>41944</v>
       </c>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="H348" s="4"/>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" s="5">
         <v>41974</v>
       </c>
@@ -8887,7 +8887,7 @@
       </c>
       <c r="H349" s="4"/>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" s="5">
         <v>42005</v>
       </c>
@@ -8911,7 +8911,7 @@
       </c>
       <c r="H350" s="4"/>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" s="5">
         <v>42036</v>
       </c>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="H351" s="4"/>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" s="5">
         <v>42064</v>
       </c>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="H352" s="4"/>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" s="5">
         <v>42095</v>
       </c>
@@ -8983,7 +8983,7 @@
       </c>
       <c r="H353" s="4"/>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" s="5">
         <v>42125</v>
       </c>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="H354" s="4"/>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" s="5">
         <v>42156</v>
       </c>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="H355" s="4"/>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" s="5">
         <v>42186</v>
       </c>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="H356" s="4"/>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" s="5">
         <v>42217</v>
       </c>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="H357" s="4"/>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" s="5">
         <v>42248</v>
       </c>
@@ -9103,7 +9103,7 @@
       </c>
       <c r="H358" s="4"/>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" s="5">
         <v>42278</v>
       </c>
@@ -9127,7 +9127,7 @@
       </c>
       <c r="H359" s="4"/>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" s="5">
         <v>42309</v>
       </c>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="H360" s="4"/>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" s="5">
         <v>42339</v>
       </c>
@@ -9175,7 +9175,7 @@
       </c>
       <c r="H361" s="4"/>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" s="5">
         <v>42370</v>
       </c>
@@ -9199,7 +9199,7 @@
       </c>
       <c r="H362" s="4"/>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" s="5">
         <v>42401</v>
       </c>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="H363" s="4"/>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" s="5">
         <v>42430</v>
       </c>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="H364" s="4"/>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" s="5">
         <v>42461</v>
       </c>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="H365" s="4"/>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" s="5">
         <v>42491</v>
       </c>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="H366" s="4"/>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" s="5">
         <v>42522</v>
       </c>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="H367" s="4"/>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" s="5">
         <v>42552</v>
       </c>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="H368" s="4"/>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" s="5">
         <v>42583</v>
       </c>
@@ -9367,7 +9367,7 @@
       </c>
       <c r="H369" s="4"/>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" s="5">
         <v>42614</v>
       </c>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="H370" s="4"/>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" s="5">
         <v>42644</v>
       </c>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="H371" s="4"/>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" s="5">
         <v>42675</v>
       </c>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="H372" s="4"/>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" s="5">
         <v>42705</v>
       </c>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="H373" s="4"/>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" s="5">
         <v>42736</v>
       </c>
@@ -9487,7 +9487,7 @@
       </c>
       <c r="H374" s="4"/>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" s="5">
         <v>42767</v>
       </c>
@@ -9511,7 +9511,7 @@
       </c>
       <c r="H375" s="4"/>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" s="5">
         <v>42795</v>
       </c>
@@ -9535,7 +9535,7 @@
       </c>
       <c r="H376" s="4"/>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" s="5">
         <v>42826</v>
       </c>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="H377" s="4"/>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" s="5">
         <v>42856</v>
       </c>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="H378" s="4"/>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" s="5">
         <v>42887</v>
       </c>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="H379" s="4"/>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" s="5">
         <v>42917</v>
       </c>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="H380" s="4"/>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" s="5">
         <v>42948</v>
       </c>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="H381" s="4"/>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" s="5">
         <v>42979</v>
       </c>
@@ -9679,7 +9679,7 @@
       </c>
       <c r="H382" s="4"/>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" s="5">
         <v>43009</v>
       </c>
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H383" s="4"/>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" s="5">
         <v>43040</v>
       </c>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="H384" s="4"/>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" s="5">
         <v>43070</v>
       </c>
@@ -9751,7 +9751,7 @@
       </c>
       <c r="H385" s="4"/>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" s="5">
         <v>43101</v>
       </c>
@@ -9775,7 +9775,7 @@
       </c>
       <c r="H386" s="4"/>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" s="5">
         <v>43132</v>
       </c>
@@ -9799,7 +9799,7 @@
       </c>
       <c r="H387" s="4"/>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" s="5">
         <v>43160</v>
       </c>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="H388" s="4"/>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" s="5">
         <v>43191</v>
       </c>
@@ -9847,7 +9847,7 @@
       </c>
       <c r="H389" s="4"/>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" s="5">
         <v>43221</v>
       </c>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="H390" s="4"/>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" s="5">
         <v>43252</v>
       </c>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="H391" s="4"/>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" s="5">
         <v>43282</v>
       </c>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="H392" s="4"/>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" s="5">
         <v>43313</v>
       </c>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H393" s="4"/>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" s="5">
         <v>43344</v>
       </c>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="H394" s="4"/>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" s="5">
         <v>43374</v>
       </c>
@@ -9991,7 +9991,7 @@
       </c>
       <c r="H395" s="4"/>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" s="5">
         <v>43405</v>
       </c>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="H396" s="4"/>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" s="5">
         <v>43435</v>
       </c>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="H397" s="4"/>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" s="5">
         <v>43466</v>
       </c>
@@ -10063,7 +10063,7 @@
       </c>
       <c r="H398" s="4"/>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" s="5">
         <v>43497</v>
       </c>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="H399" s="4"/>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" s="5">
         <v>43525</v>
       </c>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="H400" s="4"/>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" s="5">
         <v>43556</v>
       </c>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="H401" s="4"/>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" s="5">
         <v>43586</v>
       </c>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="H402" s="4"/>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" s="5">
         <v>43617</v>
       </c>
@@ -10183,7 +10183,7 @@
       </c>
       <c r="H403" s="4"/>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" s="5">
         <v>43647</v>
       </c>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="H404" s="4"/>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" s="5">
         <v>43678</v>
       </c>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="H405" s="4"/>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" s="5">
         <v>43709</v>
       </c>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="H406" s="4"/>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" s="5">
         <v>43739</v>
       </c>
@@ -10279,7 +10279,7 @@
       </c>
       <c r="H407" s="4"/>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" s="5">
         <v>43770</v>
       </c>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="H408" s="4"/>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" s="5">
         <v>43800</v>
       </c>
@@ -10327,7 +10327,7 @@
       </c>
       <c r="H409" s="4"/>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" s="5">
         <v>43831</v>
       </c>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="H410" s="4"/>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" s="5">
         <v>43862</v>
       </c>
@@ -10375,7 +10375,7 @@
       </c>
       <c r="H411" s="4"/>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" s="5">
         <v>43891</v>
       </c>
@@ -10399,7 +10399,7 @@
       </c>
       <c r="H412" s="4"/>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" s="5">
         <v>43922</v>
       </c>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="H413" s="4"/>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" s="5">
         <v>43952</v>
       </c>
@@ -10447,7 +10447,7 @@
       </c>
       <c r="H414" s="4"/>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" s="5">
         <v>43983</v>
       </c>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="H415" s="4"/>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" s="5">
         <v>44013</v>
       </c>
@@ -10495,7 +10495,7 @@
       </c>
       <c r="H416" s="4"/>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" s="5">
         <v>44044</v>
       </c>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="H417" s="4"/>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" s="5">
         <v>44075</v>
       </c>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="H418" s="4"/>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" s="5">
         <v>44105</v>
       </c>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="H419" s="4"/>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" s="5">
         <v>44136</v>
       </c>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="H420" s="4"/>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" s="5">
         <v>44166</v>
       </c>
@@ -10615,7 +10615,7 @@
       </c>
       <c r="H421" s="4"/>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" s="5">
         <v>44197</v>
       </c>
@@ -10639,7 +10639,7 @@
       </c>
       <c r="H422" s="4"/>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" s="5">
         <v>44228</v>
       </c>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="H423" s="4"/>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" s="5">
         <v>44256</v>
       </c>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="H424" s="4"/>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" s="5">
         <v>44287</v>
       </c>
@@ -10711,7 +10711,7 @@
       </c>
       <c r="H425" s="4"/>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" s="5">
         <v>44317</v>
       </c>
@@ -10735,7 +10735,7 @@
       </c>
       <c r="H426" s="4"/>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" s="5">
         <v>44348</v>
       </c>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="H427" s="4"/>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" s="5">
         <v>44378</v>
       </c>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="H428" s="4"/>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" s="5">
         <v>44409</v>
       </c>
@@ -10807,7 +10807,7 @@
       </c>
       <c r="H429" s="4"/>
     </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" s="5">
         <v>44440</v>
       </c>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="H430" s="4"/>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" s="5">
         <v>44470</v>
       </c>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="H431" s="4"/>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" s="5">
         <v>44501</v>
       </c>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="H432" s="4"/>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" s="5">
         <v>44531</v>
       </c>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="H433" s="4"/>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" s="5">
         <v>44562</v>
       </c>
@@ -10927,7 +10927,7 @@
       </c>
       <c r="H434" s="4"/>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" s="5">
         <v>44593</v>
       </c>
@@ -10951,7 +10951,7 @@
       </c>
       <c r="H435" s="4"/>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" s="5">
         <v>44621</v>
       </c>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="H436" s="4"/>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" s="5">
         <v>44652</v>
       </c>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="H437" s="4"/>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" s="5">
         <v>44682</v>
       </c>
@@ -11023,7 +11023,7 @@
       </c>
       <c r="H438" s="4"/>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" s="5">
         <v>44713</v>
       </c>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="H439" s="4"/>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" s="5">
         <v>44743</v>
       </c>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="H440" s="4"/>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" s="5">
         <v>44774</v>
       </c>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="H441" s="4"/>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" s="5">
         <v>44805</v>
       </c>
@@ -11119,7 +11119,7 @@
       </c>
       <c r="H442" s="4"/>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" s="5">
         <v>44835</v>
       </c>
@@ -11143,7 +11143,7 @@
       </c>
       <c r="H443" s="4"/>
     </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" s="5">
         <v>44866</v>
       </c>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H444" s="4"/>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" s="5">
         <v>44896</v>
       </c>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="H445" s="4"/>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" s="5">
         <v>44927</v>
       </c>
@@ -11215,7 +11215,7 @@
       </c>
       <c r="H446" s="4"/>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" s="5">
         <v>44958</v>
       </c>
@@ -11239,7 +11239,7 @@
       </c>
       <c r="H447" s="4"/>
     </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" s="5">
         <v>44986</v>
       </c>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="H448" s="4"/>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" s="5">
         <v>45017</v>
       </c>
@@ -11287,7 +11287,7 @@
       </c>
       <c r="H449" s="4"/>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" s="5">
         <v>45047</v>
       </c>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="H450" s="4"/>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" s="5">
         <v>45078</v>
       </c>
@@ -11335,7 +11335,7 @@
       </c>
       <c r="H451" s="4"/>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" s="5">
         <v>45108</v>
       </c>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="H452" s="4"/>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" s="5">
         <v>45139</v>
       </c>
@@ -11383,7 +11383,7 @@
       </c>
       <c r="H453" s="4"/>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" s="5">
         <v>45170</v>
       </c>
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H454" s="4"/>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" s="5">
         <v>45200</v>
       </c>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="H455" s="4"/>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" s="5">
         <v>45231</v>
       </c>
@@ -11455,7 +11455,7 @@
       </c>
       <c r="H456" s="4"/>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" s="5">
         <v>45261</v>
       </c>
@@ -11479,7 +11479,7 @@
       </c>
       <c r="H457" s="4"/>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" s="5">
         <v>45292</v>
       </c>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="H458" s="4"/>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" s="5">
         <v>45323</v>
       </c>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="H459" s="4"/>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" s="5">
         <v>45352</v>
       </c>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="H460" s="4"/>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" s="5">
         <v>45383</v>
       </c>
@@ -11575,7 +11575,7 @@
       </c>
       <c r="H461" s="4"/>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" s="5">
         <v>45413</v>
       </c>
@@ -11599,7 +11599,7 @@
       </c>
       <c r="H462" s="4"/>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" s="5">
         <v>45444</v>
       </c>
@@ -11623,7 +11623,7 @@
       </c>
       <c r="H463" s="4"/>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" s="5">
         <v>45474</v>
       </c>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="H464" s="4"/>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" s="5">
         <v>45505</v>
       </c>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="H465" s="4"/>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" s="5">
         <v>45536</v>
       </c>
@@ -11695,7 +11695,7 @@
       </c>
       <c r="H466" s="4"/>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" s="5">
         <v>45566</v>
       </c>
@@ -11719,7 +11719,7 @@
       </c>
       <c r="H467" s="4"/>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" s="5">
         <v>45597</v>
       </c>
@@ -11743,7 +11743,7 @@
       </c>
       <c r="H468" s="4"/>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" s="5">
         <v>45627</v>
       </c>
@@ -11767,7 +11767,7 @@
       </c>
       <c r="H469" s="4"/>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" s="5">
         <v>45658</v>
       </c>
@@ -11791,7 +11791,7 @@
       </c>
       <c r="H470" s="4"/>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" s="5">
         <v>45689</v>
       </c>
@@ -11815,7 +11815,7 @@
       </c>
       <c r="H471" s="4"/>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" s="5">
         <v>45717</v>
       </c>
@@ -11839,7 +11839,7 @@
       </c>
       <c r="H472" s="4"/>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" s="5">
         <v>45748</v>
       </c>
@@ -11863,7 +11863,7 @@
       </c>
       <c r="H473" s="4"/>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" s="5">
         <v>45778</v>
       </c>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="H474" s="4"/>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" s="5">
         <v>45809</v>
       </c>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="H475" s="4"/>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" s="5">
         <v>45839</v>
       </c>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="H476" s="4"/>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" s="5">
         <v>45870</v>
       </c>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="H477" s="4"/>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" s="5">
         <v>45901</v>
       </c>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="H478" s="4"/>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" s="5">
         <v>45931</v>
       </c>
@@ -12007,7 +12007,7 @@
       </c>
       <c r="H479" s="4"/>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" s="5">
         <v>45962</v>
       </c>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="H480" s="4"/>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" s="5">
         <v>45992</v>
       </c>
@@ -12056,9 +12056,10 @@
       <c r="H481" s="4"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G481">
+  <sortState ref="A2:G481">
     <sortCondition ref="B2:B481"/>
   </sortState>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12066,9 +12067,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{651FE52F-B836-C048-8E04-77D870B1C558}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -12076,7 +12077,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>11</v>
       </c>
@@ -12085,6 +12086,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{576E4B7C-CE33-3440-8ED0-74DD24CFDFDE}"/>
   </hyperlinks>

--- a/data/macro/China/China CPI.xlsx
+++ b/data/macro/China/China CPI.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\China\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BC17E5-A040-4707-87BD-ACB8F56F9255}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE1071B-7B1A-4779-9AF7-72D16B3F4A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6705" yWindow="3255" windowWidth="27645" windowHeight="16680" xr2:uid="{C2D375C2-0F84-A74D-B79F-82236B74EEEF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C2D375C2-0F84-A74D-B79F-82236B74EEEF}"/>
   </bookViews>
   <sheets>
     <sheet name="CNCPIYOY" sheetId="1" r:id="rId1"/>
-    <sheet name="info" sheetId="2" r:id="rId2"/>
+    <sheet name="fig" sheetId="3" r:id="rId2"/>
+    <sheet name="info" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="14">
   <si>
     <t>Time</t>
   </si>
@@ -77,8 +78,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="179" formatCode="0.0%"/>
-    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="0.0%"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -169,14 +170,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -196,6 +197,3769 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>CNCPIYOY</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>CNCPIYOY!$B$2:$B$484</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="483"/>
+                <c:pt idx="0">
+                  <c:v>31444</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31472</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>31503</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31533</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>31564</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31594</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>31625</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>31656</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31686</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>31717</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>31747</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>31778</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>31809</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>31837</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>31868</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>31898</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>31929</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>31959</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>31990</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>32021</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>32051</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>32082</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>32112</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>32143</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>32174</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>32203</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>32234</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>32264</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>32295</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>32325</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>32356</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32387</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>32417</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>32448</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>32478</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>32509</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>32540</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>32568</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>32599</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>32629</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>32660</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>32690</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>32721</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>32752</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>32782</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>32813</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>32843</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>32874</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>32905</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>32933</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>32964</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>32994</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>33025</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>33055</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>33086</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>33117</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>33147</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>33178</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>33208</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>33239</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>33270</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>33298</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>33329</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>33359</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>33390</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>33420</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>33451</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>33482</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>33512</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>33543</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>33573</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>33604</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>33635</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>33664</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>33695</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>33725</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>33756</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>33786</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>33817</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>33848</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>33878</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>33909</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>33939</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>33970</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>34001</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>34029</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>34060</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>34090</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>34121</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>34151</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>34182</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>34213</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>34243</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>34274</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>34304</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>34335</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>34366</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>34394</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>34425</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>34455</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>34486</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>34516</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>34547</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>34578</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>34608</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>34639</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>34669</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>34700</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>34731</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>34759</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>34790</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>34820</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>34851</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>34881</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>34912</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>34943</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>34973</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>35004</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>35034</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>35065</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>35096</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>35125</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>35156</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>35186</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>35217</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>35247</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>35278</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>35309</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>35339</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>35370</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>35400</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>35431</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>35462</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>35490</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>35521</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>35551</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>35582</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>35612</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>35643</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>35674</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>35704</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>35735</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>35765</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>35796</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>35827</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>35855</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>35886</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>35916</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>35947</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>35977</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>36008</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>36039</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>36069</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>36100</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>36130</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>36161</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>36192</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>36220</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>36251</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>36281</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>36312</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>36342</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>36373</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>36404</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>36434</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>36465</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>36495</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>36526</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>36557</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>36586</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>36617</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>36647</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>36678</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>36708</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>36739</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>36770</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>36800</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>36831</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>36861</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>36892</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>36923</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>36951</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>36982</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>37012</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>37043</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>37073</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>37104</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>37135</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>37165</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>37196</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>37226</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>37257</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>37288</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>37316</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>37347</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>37377</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>37408</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>37438</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>37469</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>37500</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>37530</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>37561</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>37591</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>37622</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>37653</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>37681</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>37712</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>37742</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>37773</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>37803</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>37834</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>37865</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>37895</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>37926</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>37956</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>37987</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>38018</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>38047</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>38078</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>38108</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>38139</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>38169</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>38200</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>38231</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>38261</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>38292</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>38322</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>38353</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>38384</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>38412</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>38443</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>38473</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>38504</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>38534</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>38565</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>38596</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>38626</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>38657</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>38687</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>38718</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>38749</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>38777</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>38808</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>38838</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>38869</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>38899</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>38930</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>38961</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>38991</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>39022</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>39052</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>39083</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>39114</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>39142</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>39173</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>39203</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>39234</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>39264</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>39295</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>39326</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>39356</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>39387</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>39417</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>39448</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>39479</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>39508</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>39539</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>39569</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>39600</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>39630</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>39661</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>39692</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>39722</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>39753</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>39783</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>39814</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>39845</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>39873</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>39904</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>39934</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>39965</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>39995</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>40026</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>40057</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>40087</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>40118</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>40148</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>40179</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>40210</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>40238</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>40269</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>40299</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>40330</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>40360</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>40391</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>40422</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>40452</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>40483</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>40523</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>40563</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>40589</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>40613</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>40648</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>40674</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>40708</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>40733</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>40764</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>40795</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>40830</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>40856</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>40886</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>40920</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>40948</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>40977</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>41008</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>41040</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>41069</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>41099</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>41130</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>41161</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>41197</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>41222</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>41252</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>41285</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>41314</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>41342</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>41373</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>41403</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>41434</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>41464</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>41495</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>41526</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>41561</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>41587</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>41617</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>41648</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>41684</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>41707</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>41740</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>41768</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>41800</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>41829</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>41860</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>41893</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>41927</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>41953</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>41983</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>42013</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>42045</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>42073</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>42104</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>42133</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>42164</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>42194</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>42225</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>42257</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>42291</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>42318</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>42347</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>42378</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>42418</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>42439</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>42471</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>42500</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>42530</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>42561</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>42591</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>42622</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>42657</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>42683</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>42713</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>42745</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>42780</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>42803</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>42837</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>42865</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>42895</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>42926</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>42956</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>42987</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>43024</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>43048</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>43078</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>43110</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>43140</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>43168</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>43201</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>43230</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>43260</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>43291</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>43321</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>43353</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>43389</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>43413</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>43443</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>43475</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>43511</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>43533</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>43566</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>43594</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>43628</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>43656</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>43686</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>43718</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>43753</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>43778</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>43809</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>43839</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>43871</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>43900</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>43931</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>43963</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>43992</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>44021</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>44053</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>44083</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>44119</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>44145</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>44174</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>44207</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>44237</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>44265</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>44295</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>44327</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>44356</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>44386</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>44417</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>44448</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>44483</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>44510</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>44539</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>44573</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>44608</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>44629</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>44662</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>44692</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>44722</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>44751</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>44783</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>44813</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>44848</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>44874</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>44904</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>44938</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>44967</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>44994</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>45027</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>45057</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>45086</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>45117</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>45147</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>45178</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>45212</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>45239</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>45269</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>45303</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>45330</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>45360</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>45393</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>45423</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>45455</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>45483</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>45513</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>45544</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>45578</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>45605</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>45635</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>45666</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>45697</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>45725</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>45757</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>45787</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>45817</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>45847</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>45878</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>45910</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>45945</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>45970</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>46001</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>46031</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>46090</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>46122</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>CNCPIYOY!$E$2:$E$484</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="483"/>
+                <c:pt idx="0">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>8.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7.6999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>8.3000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>8.8999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.104</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.113</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.122</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.14199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.16300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.192</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.23599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.26400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.27100000000000002</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.26800000000000002</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.27900000000000003</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.27400000000000002</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.28399999999999997</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.27100000000000002</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.26600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.249</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.22800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.19400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.153</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.115</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8.5999999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>7.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>8.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>8.7999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.10299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.108</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.122</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.126</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.151</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.16200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.16400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.157</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.159</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.16700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.188</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.21099999999999999</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.23200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.224</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.217</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.21299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.22600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>0.24</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>0.25800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.27300000000000002</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.27700000000000002</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>0.27500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>0.255</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>0.24099999999999999</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.224</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>0.21299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>0.20699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.20300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>0.182</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>0.16700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>0.14499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>0.13200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>0.121</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>0.112</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>0.10100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>9.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>9.8000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>9.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>8.8999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>8.5999999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>8.3000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>8.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>-1E-3</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>-3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>-0.01</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>-1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>-1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>-1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>-1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>-1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>-1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>-0.01</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>-1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>-1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>-1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>-2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>-2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>-2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>-1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>-1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>-8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>-6.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>-8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>-0.01</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>-2E-3</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>-2E-3</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>-3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>-1E-3</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>-3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>-3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>-0.01</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>-8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>-1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>-1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>-8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>-8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>-7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>-7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>-8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>-7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>-4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>8.6999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>8.3000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>7.6999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>-1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>-1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>-1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>-1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>-1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>-1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>-1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>-8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>-5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>6.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>2.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>3.1E-2</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.02</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>1.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>2.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>2.1999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>1.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>2.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>1.7000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>-5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>-3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>-2E-3</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>1.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>2.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>1.4999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>2.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>2.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>1.6E-2</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>1.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>2.1000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>-3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>-2E-3</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>-5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>-3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>-8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>6.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>-7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>-1E-3</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>-1E-3</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>-1E-3</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>-4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>-3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>1.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>0.01</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1BD0-486C-BA85-A857DB8AE826}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2137139919"/>
+        <c:axId val="2137149999"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="2137139919"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="46387"/>
+          <c:min val="42005"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2137149999"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="2137149999"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="6.0000000000000012E-2"/>
+          <c:min val="-1.0000000000000002E-2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2137139919"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D91E0D78-FCBE-41F3-A69E-C8382539E2E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -515,15 +4279,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01A2DF88-805C-2E4E-A3EC-9F545567B7EC}">
-  <dimension ref="A1:I482"/>
-  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I484"/>
+  <sheetFormatPr defaultColWidth="10.81640625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" style="6"/>
-    <col min="2" max="2" width="12.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" style="13"/>
-    <col min="4" max="4" width="10.77734375" style="9"/>
-    <col min="5" max="7" width="10.77734375" style="11"/>
-    <col min="8" max="16384" width="10.77734375" style="4"/>
+    <col min="1" max="1" width="10.81640625" style="6"/>
+    <col min="2" max="2" width="12.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" style="13"/>
+    <col min="4" max="4" width="10.81640625" style="9"/>
+    <col min="5" max="7" width="10.81640625" style="11"/>
+    <col min="8" max="16384" width="10.81640625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -12094,8 +15858,54 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A483" s="6">
+        <v>46054</v>
+      </c>
+      <c r="B483" s="6">
+        <v>46090</v>
+      </c>
+      <c r="C483" s="13">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D483" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E483" s="11">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="F483" s="11">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="G483" s="11">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A484" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B484" s="6">
+        <v>46122</v>
+      </c>
+      <c r="C484" s="13">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D484" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E484" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="F484" s="11">
+        <v>1.2E-2</v>
+      </c>
+      <c r="G484" s="11">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="A2:G481">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G481">
     <sortCondition ref="B2:B481"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -12105,11 +15915,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91024DA1-00F0-4602-9985-01AD43B6ED3C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{651FE52F-B836-C048-8E04-77D870B1C558}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>9</v>
       </c>
@@ -12117,7 +15938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>11</v>
       </c>
